--- a/MINI PROJECT/3CSN01_Mini Project Details.xlsx
+++ b/MINI PROJECT/3CSN01_Mini Project Details.xlsx
@@ -748,7 +748,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -760,10 +760,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -904,14 +906,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -919,7 +915,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -928,10 +925,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1218,7 +1220,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1227,7 +1229,7 @@
     <col min="6" max="6" width="58.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1240,14 +1242,14 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="14" t="s">
         <v>201</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="45">
+    <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
@@ -1260,10 +1262,10 @@
       <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="19" t="s">
         <v>217</v>
       </c>
       <c r="G2" s="4"/>
@@ -1273,7 +1275,7 @@
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" spans="1:12" ht="45">
+    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
@@ -1286,8 +1288,8 @@
       <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="17"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="16"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -1295,7 +1297,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="1:12" ht="30">
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>188</v>
       </c>
@@ -1308,8 +1310,8 @@
       <c r="D4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="17"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="16"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -1317,7 +1319,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" ht="51" customHeight="1" thickBot="1">
+    <row r="5" spans="1:12" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>15</v>
       </c>
@@ -1330,8 +1332,8 @@
       <c r="D5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="17"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -1339,7 +1341,7 @@
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12" ht="45">
+    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>19</v>
       </c>
@@ -1352,10 +1354,10 @@
       <c r="D6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="15" t="s">
         <v>218</v>
       </c>
       <c r="G6" s="4"/>
@@ -1365,7 +1367,7 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" ht="30">
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>23</v>
       </c>
@@ -1378,8 +1380,8 @@
       <c r="D7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="17"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="16"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -1387,7 +1389,7 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" ht="30">
+    <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>190</v>
       </c>
@@ -1400,8 +1402,8 @@
       <c r="D8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="17"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -1409,7 +1411,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" ht="42.75" customHeight="1" thickBot="1">
+    <row r="9" spans="1:12" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>30</v>
       </c>
@@ -1422,8 +1424,8 @@
       <c r="D9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="17"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1431,7 +1433,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" ht="30">
+    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>34</v>
       </c>
@@ -1444,10 +1446,10 @@
       <c r="D10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="15" t="s">
         <v>219</v>
       </c>
       <c r="G10" s="4"/>
@@ -1457,7 +1459,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" ht="30">
+    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>38</v>
       </c>
@@ -1470,8 +1472,8 @@
       <c r="D11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="17"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="16"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -1479,8 +1481,8 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" ht="30">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>208</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -1492,8 +1494,8 @@
       <c r="D12" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="17"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="16"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -1501,7 +1503,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" ht="35.25" customHeight="1" thickBot="1">
+    <row r="13" spans="1:12" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>45</v>
       </c>
@@ -1514,8 +1516,8 @@
       <c r="D13" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="18"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -1523,7 +1525,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" ht="30">
+    <row r="14" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>49</v>
       </c>
@@ -1536,10 +1538,10 @@
       <c r="D14" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="15" t="s">
         <v>220</v>
       </c>
       <c r="G14" s="4"/>
@@ -1549,7 +1551,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" ht="45">
+    <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>53</v>
       </c>
@@ -1562,8 +1564,8 @@
       <c r="D15" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="17"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="16"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -1571,8 +1573,8 @@
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:12" ht="30">
-      <c r="A16" s="15" t="s">
+    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>207</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -1584,8 +1586,8 @@
       <c r="D16" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="16"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1593,15 +1595,15 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12" ht="40.5" customHeight="1" thickBot="1">
+    <row r="17" spans="1:12" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="5" t="s">
         <v>187</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="17"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -1609,7 +1611,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:12" ht="30">
+    <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>60</v>
       </c>
@@ -1622,10 +1624,10 @@
       <c r="D18" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="15" t="s">
         <v>222</v>
       </c>
       <c r="G18" s="4"/>
@@ -1635,7 +1637,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12" ht="30">
+    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>192</v>
       </c>
@@ -1648,8 +1650,8 @@
       <c r="D19" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="17"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="16"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -1657,7 +1659,7 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" ht="30">
+    <row r="20" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>67</v>
       </c>
@@ -1670,8 +1672,8 @@
       <c r="D20" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="17"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="16"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -1679,7 +1681,7 @@
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12" ht="43.5" customHeight="1" thickBot="1">
+    <row r="21" spans="1:12" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>71</v>
       </c>
@@ -1692,8 +1694,8 @@
       <c r="D21" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="18"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="17"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -1701,8 +1703,8 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:12" ht="30">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>206</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -1714,10 +1716,10 @@
       <c r="D22" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="15" t="s">
         <v>223</v>
       </c>
       <c r="G22" s="4"/>
@@ -1727,7 +1729,7 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:12" ht="30">
+    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>78</v>
       </c>
@@ -1740,8 +1742,8 @@
       <c r="D23" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="17"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="16"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -1749,7 +1751,7 @@
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12" ht="30">
+    <row r="24" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>82</v>
       </c>
@@ -1762,8 +1764,8 @@
       <c r="D24" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="17"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="16"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -1771,7 +1773,7 @@
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12" ht="45.75" thickBot="1">
+    <row r="25" spans="1:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>86</v>
       </c>
@@ -1784,8 +1786,8 @@
       <c r="D25" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="17"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -1793,7 +1795,7 @@
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="1:12" ht="30">
+    <row r="26" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>90</v>
       </c>
@@ -1806,10 +1808,10 @@
       <c r="D26" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="F26" s="19" t="s">
+      <c r="F26" s="15" t="s">
         <v>224</v>
       </c>
       <c r="G26" s="4"/>
@@ -1819,7 +1821,7 @@
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="1:12" ht="45">
+    <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>94</v>
       </c>
@@ -1832,8 +1834,8 @@
       <c r="D27" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="17"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="16"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -1841,8 +1843,8 @@
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="1:12" ht="30">
-      <c r="A28" s="14" t="s">
+    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>98</v>
       </c>
       <c r="B28" s="7" t="s">
@@ -1851,11 +1853,11 @@
       <c r="C28" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="17"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="16"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -1863,8 +1865,8 @@
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="1:12" ht="51.75" customHeight="1" thickBot="1">
-      <c r="A29" s="15" t="s">
+    <row r="29" spans="1:12" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
         <v>205</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -1876,8 +1878,8 @@
       <c r="D29" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="17"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -1885,7 +1887,7 @@
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:12" ht="30">
+    <row r="30" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>193</v>
       </c>
@@ -1898,10 +1900,10 @@
       <c r="D30" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="F30" s="15" t="s">
         <v>229</v>
       </c>
       <c r="G30" s="4"/>
@@ -1911,7 +1913,7 @@
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:12" ht="30">
+    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>108</v>
       </c>
@@ -1924,8 +1926,8 @@
       <c r="D31" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="11"/>
-      <c r="F31" s="17"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="16"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
@@ -1933,7 +1935,7 @@
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
     </row>
-    <row r="32" spans="1:12" ht="30">
+    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>112</v>
       </c>
@@ -1946,8 +1948,8 @@
       <c r="D32" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E32" s="11"/>
-      <c r="F32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="16"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -1955,7 +1957,7 @@
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" spans="1:12" ht="104.25" customHeight="1" thickBot="1">
+    <row r="33" spans="1:12" ht="104.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>116</v>
       </c>
@@ -1968,8 +1970,8 @@
       <c r="D33" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="11"/>
-      <c r="F33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="17"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
@@ -1977,7 +1979,7 @@
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:12" ht="30">
+    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>120</v>
       </c>
@@ -1990,10 +1992,10 @@
       <c r="D34" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="F34" s="15" t="s">
         <v>225</v>
       </c>
       <c r="G34" s="4"/>
@@ -2003,7 +2005,7 @@
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" spans="1:12" ht="30">
+    <row r="35" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>124</v>
       </c>
@@ -2016,8 +2018,8 @@
       <c r="D35" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="11"/>
-      <c r="F35" s="17"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="16"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
@@ -2025,7 +2027,7 @@
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
     </row>
-    <row r="36" spans="1:12" ht="30">
+    <row r="36" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>194</v>
       </c>
@@ -2038,8 +2040,8 @@
       <c r="D36" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="E36" s="11"/>
-      <c r="F36" s="17"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="16"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
@@ -2047,7 +2049,7 @@
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="1:12" ht="48.75" customHeight="1" thickBot="1">
+    <row r="37" spans="1:12" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>199</v>
       </c>
@@ -2056,8 +2058,8 @@
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="17"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -2065,8 +2067,8 @@
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="1:12" ht="45">
-      <c r="A38" s="15" t="s">
+    <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
         <v>204</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -2078,10 +2080,10 @@
       <c r="D38" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="F38" s="15" t="s">
         <v>226</v>
       </c>
       <c r="G38" s="4"/>
@@ -2091,7 +2093,7 @@
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
     </row>
-    <row r="39" spans="1:12" ht="30">
+    <row r="39" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>134</v>
       </c>
@@ -2104,8 +2106,8 @@
       <c r="D39" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E39" s="11"/>
-      <c r="F39" s="17"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="16"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
@@ -2113,7 +2115,7 @@
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" spans="1:12" ht="30">
+    <row r="40" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>138</v>
       </c>
@@ -2126,8 +2128,8 @@
       <c r="D40" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E40" s="11"/>
-      <c r="F40" s="17"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="16"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -2135,7 +2137,7 @@
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
     </row>
-    <row r="41" spans="1:12" ht="43.5" customHeight="1" thickBot="1">
+    <row r="41" spans="1:12" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>142</v>
       </c>
@@ -2148,8 +2150,8 @@
       <c r="D41" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="E41" s="11"/>
-      <c r="F41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="17"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -2157,7 +2159,7 @@
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
     </row>
-    <row r="42" spans="1:12" ht="30">
+    <row r="42" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>196</v>
       </c>
@@ -2170,10 +2172,10 @@
       <c r="D42" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="F42" s="19" t="s">
+      <c r="F42" s="15" t="s">
         <v>227</v>
       </c>
       <c r="G42" s="4"/>
@@ -2183,7 +2185,7 @@
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
     </row>
-    <row r="43" spans="1:12" ht="30">
+    <row r="43" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>148</v>
       </c>
@@ -2196,8 +2198,8 @@
       <c r="D43" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="17"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="16"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -2205,7 +2207,7 @@
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
     </row>
-    <row r="44" spans="1:12" ht="83.25" customHeight="1" thickBot="1">
+    <row r="44" spans="1:12" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>152</v>
       </c>
@@ -2218,8 +2220,8 @@
       <c r="D44" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="E44" s="13"/>
-      <c r="F44" s="18"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="17"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -2227,7 +2229,7 @@
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
     </row>
-    <row r="45" spans="1:12" ht="15" customHeight="1">
+    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>156</v>
       </c>
@@ -2240,10 +2242,10 @@
       <c r="D45" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="F45" s="19" t="s">
+      <c r="F45" s="15" t="s">
         <v>228</v>
       </c>
       <c r="G45" s="4"/>
@@ -2253,8 +2255,8 @@
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
     </row>
-    <row r="46" spans="1:12" ht="30">
-      <c r="A46" s="15" t="s">
+    <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
         <v>203</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -2266,16 +2268,16 @@
       <c r="D46" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E46" s="11"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" spans="1:12" ht="30">
+    <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>163</v>
       </c>
@@ -2288,8 +2290,8 @@
       <c r="D47" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="E47" s="11"/>
-      <c r="F47" s="17"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="16"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -2297,7 +2299,7 @@
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
     </row>
-    <row r="48" spans="1:12" ht="74.25" customHeight="1" thickBot="1">
+    <row r="48" spans="1:12" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>167</v>
       </c>
@@ -2310,8 +2312,8 @@
       <c r="D48" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E48" s="11"/>
-      <c r="F48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="17"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -2319,7 +2321,7 @@
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
     </row>
-    <row r="49" spans="1:12" ht="30">
+    <row r="49" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>171</v>
       </c>
@@ -2332,10 +2334,10 @@
       <c r="D49" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="F49" s="19" t="s">
+      <c r="F49" s="15" t="s">
         <v>231</v>
       </c>
       <c r="G49" s="4"/>
@@ -2345,7 +2347,7 @@
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
     </row>
-    <row r="50" spans="1:12" ht="45">
+    <row r="50" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>175</v>
       </c>
@@ -2358,8 +2360,8 @@
       <c r="D50" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E50" s="11"/>
-      <c r="F50" s="17"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="16"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -2367,7 +2369,7 @@
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
     </row>
-    <row r="51" spans="1:12" ht="30">
+    <row r="51" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>179</v>
       </c>
@@ -2380,8 +2382,8 @@
       <c r="D51" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="E51" s="11"/>
-      <c r="F51" s="17"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="16"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
@@ -2389,7 +2391,7 @@
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
     </row>
-    <row r="52" spans="1:12" ht="48.75" customHeight="1" thickBot="1">
+    <row r="52" spans="1:12" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>197</v>
       </c>
@@ -2402,8 +2404,8 @@
       <c r="D52" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="E52" s="11"/>
-      <c r="F52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="17"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -2411,61 +2413,56 @@
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B58">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="3:3">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="70" spans="3:3">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>186</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="F45:F48"/>
-    <mergeCell ref="F49:F52"/>
-    <mergeCell ref="E49:E52"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="E18:E21"/>
     <mergeCell ref="F22:F25"/>
     <mergeCell ref="F26:F29"/>
     <mergeCell ref="F30:F33"/>
@@ -2473,15 +2470,20 @@
     <mergeCell ref="E26:E29"/>
     <mergeCell ref="E30:E33"/>
     <mergeCell ref="E34:E37"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="F45:F48"/>
+    <mergeCell ref="F49:F52"/>
+    <mergeCell ref="E49:E52"/>
     <mergeCell ref="E38:E41"/>
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E45:E48"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="E14:E17"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="E22:E25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/MINI PROJECT/3CSN01_Mini Project Details.xlsx
+++ b/MINI PROJECT/3CSN01_Mini Project Details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="235">
   <si>
     <t>STUDENT_NAME</t>
   </si>
@@ -178,9 +178,6 @@
     <t>KALAVATALA NAGA SAI CHARAN</t>
   </si>
   <si>
-    <t>20241CSN0021</t>
-  </si>
-  <si>
     <t>8919053899</t>
   </si>
   <si>
@@ -575,9 +572,6 @@
   </si>
   <si>
     <t>incomplete</t>
-  </si>
-  <si>
-    <t>20241CSN0023</t>
   </si>
   <si>
     <t>SREDHA S NAMBIAR (Lead)</t>
@@ -742,6 +736,21 @@
 It provides a centralized web platform where candidates can apply for open positions, upload resumes, and track their application status, while HR administrators can manage job listings, schedule interviews, evaluate applicants, and issue offer letters—all in one integrated system.
 Beyond recruitment, the HRMS also handles employee record management, attendance tracking, leave approvals, and performance reviews, ensuring all HR operations are transparent and efficient.
 The website reduces paperwork, enhances collaboration among HR teams, and maintains a secure database of employee information.</t>
+  </si>
+  <si>
+    <t>cancelled</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>repeat</t>
+  </si>
+  <si>
+    <t>20241CSN0023 g5</t>
+  </si>
+  <si>
+    <t>20241CSN0021 g6</t>
   </si>
 </sst>
 </file>
@@ -916,6 +925,12 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -925,14 +940,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1243,10 +1252,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.25">
@@ -1262,13 +1271,15 @@
       <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="G2" s="4"/>
+      <c r="E2" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>230</v>
+      </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -1288,8 +1299,8 @@
       <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="16"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="18"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -1299,7 +1310,7 @@
     </row>
     <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>12</v>
@@ -1310,8 +1321,8 @@
       <c r="D4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="16"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -1332,8 +1343,8 @@
       <c r="D5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="17"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="19"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -1354,13 +1365,15 @@
       <c r="D6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="G6" s="4"/>
+      <c r="E6" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>230</v>
+      </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -1380,8 +1393,8 @@
       <c r="D7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="16"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="18"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -1391,7 +1404,7 @@
     </row>
     <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>27</v>
@@ -1402,8 +1415,8 @@
       <c r="D8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="18"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -1424,8 +1437,8 @@
       <c r="D9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="17"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="19"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1446,11 +1459,11 @@
       <c r="D10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>219</v>
+      <c r="E10" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>217</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -1472,9 +1485,11 @@
       <c r="D11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="4"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="4" t="s">
+        <v>231</v>
+      </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
@@ -1483,7 +1498,7 @@
     </row>
     <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>42</v>
@@ -1494,8 +1509,8 @@
       <c r="D12" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -1516,8 +1531,8 @@
       <c r="D13" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="17"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -1538,11 +1553,11 @@
       <c r="D14" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>220</v>
+      <c r="E14" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>218</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -1556,17 +1571,19 @@
         <v>53</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="4"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="4" t="s">
+        <v>232</v>
+      </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -1575,19 +1592,19 @@
     </row>
     <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="18"/>
-      <c r="F16" s="16"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1598,12 +1615,12 @@
     <row r="17" spans="1:12" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="5" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="17"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="19"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -1613,22 +1630,22 @@
     </row>
     <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>222</v>
+      <c r="E18" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>220</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -1639,20 +1656,22 @@
     </row>
     <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="4"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="4" t="s">
+        <v>231</v>
+      </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
@@ -1661,19 +1680,19 @@
     </row>
     <row r="20" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="20"/>
-      <c r="F20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="18"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -1683,19 +1702,19 @@
     </row>
     <row r="21" spans="1:12" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="20"/>
-      <c r="F21" s="17"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="19"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -1705,22 +1724,22 @@
     </row>
     <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="D22" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>223</v>
+      <c r="E22" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>221</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -1731,19 +1750,19 @@
     </row>
     <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="18"/>
-      <c r="F23" s="16"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="18"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -1753,19 +1772,19 @@
     </row>
     <row r="24" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="16"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="18"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -1775,19 +1794,19 @@
     </row>
     <row r="25" spans="1:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="17"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -1797,22 +1816,22 @@
     </row>
     <row r="26" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>224</v>
+      <c r="E26" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>222</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -1823,19 +1842,19 @@
     </row>
     <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E27" s="18"/>
-      <c r="F27" s="16"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -1845,19 +1864,19 @@
     </row>
     <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="D28" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="16"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -1867,19 +1886,19 @@
     </row>
     <row r="29" spans="1:12" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="D29" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="17"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="19"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -1889,22 +1908,22 @@
     </row>
     <row r="30" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="D30" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>229</v>
+      <c r="E30" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>227</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -1915,19 +1934,19 @@
     </row>
     <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E31" s="18"/>
-      <c r="F31" s="16"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="18"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
@@ -1937,19 +1956,19 @@
     </row>
     <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E32" s="18"/>
-      <c r="F32" s="16"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="18"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -1959,19 +1978,19 @@
     </row>
     <row r="33" spans="1:12" ht="104.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="17"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="19"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
@@ -1981,22 +2000,22 @@
     </row>
     <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D34" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>225</v>
+      <c r="E34" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>223</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -2007,19 +2026,19 @@
     </row>
     <row r="35" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="E35" s="18"/>
-      <c r="F35" s="16"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
@@ -2029,19 +2048,19 @@
     </row>
     <row r="36" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="D36" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D36" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="E36" s="18"/>
-      <c r="F36" s="16"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
@@ -2051,15 +2070,15 @@
     </row>
     <row r="37" spans="1:12" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="17"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="19"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -2069,22 +2088,22 @@
     </row>
     <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B38" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="D38" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="D38" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>226</v>
+      <c r="E38" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>224</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -2095,19 +2114,19 @@
     </row>
     <row r="39" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" s="18"/>
-      <c r="F39" s="16"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="18"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
@@ -2117,19 +2136,19 @@
     </row>
     <row r="40" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D40" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E40" s="18"/>
-      <c r="F40" s="16"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="18"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -2139,19 +2158,19 @@
     </row>
     <row r="41" spans="1:12" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D41" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="E41" s="18"/>
-      <c r="F41" s="17"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="19"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -2161,22 +2180,22 @@
     </row>
     <row r="42" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="D42" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="D42" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="E42" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>227</v>
+      <c r="E42" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>225</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -2187,19 +2206,19 @@
     </row>
     <row r="43" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="D43" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="D43" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E43" s="20"/>
-      <c r="F43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="18"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -2209,19 +2228,19 @@
     </row>
     <row r="44" spans="1:12" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="D44" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="E44" s="20"/>
-      <c r="F44" s="17"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="19"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -2231,22 +2250,22 @@
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D45" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>228</v>
+      <c r="E45" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>226</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -2257,19 +2276,19 @@
     </row>
     <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="D46" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D46" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="E46" s="18"/>
-      <c r="F46" s="16"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="18"/>
       <c r="G46" s="11"/>
       <c r="H46" s="11"/>
       <c r="I46" s="4"/>
@@ -2279,19 +2298,19 @@
     </row>
     <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="D47" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E47" s="18"/>
-      <c r="F47" s="16"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="18"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -2301,19 +2320,19 @@
     </row>
     <row r="48" spans="1:12" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D48" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E48" s="18"/>
-      <c r="F48" s="17"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="19"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -2323,22 +2342,22 @@
     </row>
     <row r="49" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="C49" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D49" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>231</v>
+      <c r="E49" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>229</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -2349,19 +2368,19 @@
     </row>
     <row r="50" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="D50" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E50" s="18"/>
-      <c r="F50" s="16"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="18"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -2371,19 +2390,19 @@
     </row>
     <row r="51" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E51" s="18"/>
-      <c r="F51" s="16"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="18"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
@@ -2393,19 +2412,19 @@
     </row>
     <row r="52" spans="1:12" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="D52" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="D52" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="E52" s="18"/>
-      <c r="F52" s="17"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="19"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -2448,21 +2467,29 @@
     </row>
     <row r="67" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="E14:E17"/>
-    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="F45:F48"/>
+    <mergeCell ref="F49:F52"/>
+    <mergeCell ref="E49:E52"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="E45:E48"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="F18:F21"/>
     <mergeCell ref="F22:F25"/>
     <mergeCell ref="F26:F29"/>
     <mergeCell ref="F30:F33"/>
@@ -2471,19 +2498,11 @@
     <mergeCell ref="E30:E33"/>
     <mergeCell ref="E34:E37"/>
     <mergeCell ref="E22:E25"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="F45:F48"/>
-    <mergeCell ref="F49:F52"/>
-    <mergeCell ref="E49:E52"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="E45:E48"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="E18:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/MINI PROJECT/3CSN01_Mini Project Details.xlsx
+++ b/MINI PROJECT/3CSN01_Mini Project Details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="235">
   <si>
     <t>STUDENT_NAME</t>
   </si>
@@ -40,9 +40,6 @@
     <t>KAPPAGANTHULA.20241CSN0001@presidencyuniversity.in</t>
   </si>
   <si>
-    <t>PRABHAKAR KUMAR THAKUR</t>
-  </si>
-  <si>
     <t>20241CSN0005</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
     <t>SAHANA.20241CSN0019@presidencyuniversity.in</t>
   </si>
   <si>
-    <t>BHASKAR DAS</t>
-  </si>
-  <si>
     <t>20241CSN0020</t>
   </si>
   <si>
@@ -283,9 +277,6 @@
     <t>CINGATHALAM.20241CSN0036@presidencyuniversity.in</t>
   </si>
   <si>
-    <t>PALLAVI R</t>
-  </si>
-  <si>
     <t>20241CSN0037</t>
   </si>
   <si>
@@ -415,9 +406,6 @@
     <t>MUHAMMAD.20241CSN0049@presidencyuniversity.in</t>
   </si>
   <si>
-    <t>SAYED FARAAZ</t>
-  </si>
-  <si>
     <t>20241CSN0050</t>
   </si>
   <si>
@@ -526,9 +514,6 @@
     <t>IFRAH.20241CSN0060@presidencyuniversity.in</t>
   </si>
   <si>
-    <t>LAXMIKANT</t>
-  </si>
-  <si>
     <t>20241CSN0061</t>
   </si>
   <si>
@@ -574,9 +559,6 @@
     <t>incomplete</t>
   </si>
   <si>
-    <t>SREDHA S NAMBIAR (Lead)</t>
-  </si>
-  <si>
     <t>G1 Canteen / Cafe Management Module</t>
   </si>
   <si>
@@ -629,9 +611,6 @@
   </si>
   <si>
     <t>ANTHAPU MYTHRI (Lead)</t>
-  </si>
-  <si>
-    <t>CHITTEM KRISHYA (Lead)</t>
   </si>
   <si>
     <t>YUKITH M JOSEPH (Lead)</t>
@@ -750,7 +729,28 @@
     <t>20241CSN0023 g5</t>
   </si>
   <si>
-    <t>20241CSN0021 g6</t>
+    <t>20241CSN0021 g6-worst</t>
+  </si>
+  <si>
+    <t>PALLAVI R abs</t>
+  </si>
+  <si>
+    <t>SAYED FARAAZ abs</t>
+  </si>
+  <si>
+    <t>LAXMIKANT  - indisciplined during ppt</t>
+  </si>
+  <si>
+    <t>PRABHAKAR KUMAR THAKUR (Lead)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SREDHA S NAMBIAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHITTEM KRISHYA </t>
+  </si>
+  <si>
+    <t>BHASKAR DAS (Lead)</t>
   </si>
 </sst>
 </file>
@@ -796,7 +796,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -812,6 +812,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -887,7 +893,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -942,6 +948,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1252,10 +1261,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.25">
@@ -1272,14 +1281,12 @@
         <v>7</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>230</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -1288,16 +1295,16 @@
     </row>
     <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>11</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="18"/>
@@ -1309,17 +1316,17 @@
       <c r="L3" s="4"/>
     </row>
     <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>186</v>
+      <c r="A4" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="10" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>14</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="18"/>
@@ -1332,16 +1339,16 @@
     </row>
     <row r="5" spans="1:12" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="19"/>
@@ -1354,26 +1361,24 @@
     </row>
     <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="E6" s="15" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>230</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -1382,16 +1387,16 @@
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="18"/>
@@ -1404,16 +1409,16 @@
     </row>
     <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>29</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="18"/>
@@ -1426,16 +1431,16 @@
     </row>
     <row r="9" spans="1:12" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="19"/>
@@ -1448,22 +1453,22 @@
     </row>
     <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>37</v>
-      </c>
       <c r="E10" s="16" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -1473,22 +1478,22 @@
       <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="18"/>
       <c r="G11" s="4" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -1498,16 +1503,16 @@
     </row>
     <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="10" t="s">
         <v>43</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>44</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="18"/>
@@ -1520,16 +1525,16 @@
     </row>
     <row r="13" spans="1:12" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>48</v>
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="19"/>
@@ -1542,22 +1547,22 @@
     </row>
     <row r="14" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="D14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>52</v>
-      </c>
       <c r="E14" s="15" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -1568,21 +1573,21 @@
     </row>
     <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>55</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="18"/>
       <c r="G15" s="4" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -1591,17 +1596,17 @@
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>205</v>
+      <c r="A16" s="21" t="s">
+        <v>233</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="18"/>
@@ -1615,7 +1620,7 @@
     <row r="17" spans="1:12" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="9"/>
@@ -1630,22 +1635,22 @@
     </row>
     <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="D18" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>62</v>
-      </c>
       <c r="E18" s="16" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -1656,21 +1661,21 @@
     </row>
     <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>63</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="18"/>
       <c r="G19" s="4" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -1680,16 +1685,16 @@
     </row>
     <row r="20" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="D20" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>69</v>
       </c>
       <c r="E20" s="16"/>
       <c r="F20" s="18"/>
@@ -1702,16 +1707,16 @@
     </row>
     <row r="21" spans="1:12" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="D21" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="E21" s="16"/>
       <c r="F21" s="19"/>
@@ -1724,22 +1729,22 @@
     </row>
     <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>76</v>
-      </c>
       <c r="E22" s="15" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -1750,20 +1755,22 @@
     </row>
     <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="18"/>
-      <c r="G23" s="4"/>
+      <c r="G23" s="4" t="s">
+        <v>225</v>
+      </c>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
@@ -1772,16 +1779,16 @@
     </row>
     <row r="24" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="D24" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>84</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="18"/>
@@ -1794,16 +1801,16 @@
     </row>
     <row r="25" spans="1:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="D25" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="19"/>
@@ -1816,22 +1823,22 @@
     </row>
     <row r="26" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="E26" s="15" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -1842,20 +1849,22 @@
     </row>
     <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>96</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="18"/>
-      <c r="G27" s="4"/>
+      <c r="G27" s="4" t="s">
+        <v>224</v>
+      </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -1864,16 +1873,16 @@
     </row>
     <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>97</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>100</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="18"/>
@@ -1886,16 +1895,16 @@
     </row>
     <row r="29" spans="1:12" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="19"/>
@@ -1908,22 +1917,22 @@
     </row>
     <row r="30" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -1934,20 +1943,22 @@
     </row>
     <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>107</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="18"/>
-      <c r="G31" s="4"/>
+      <c r="G31" s="4" t="s">
+        <v>225</v>
+      </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
@@ -1956,16 +1967,16 @@
     </row>
     <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="18"/>
@@ -1978,16 +1989,16 @@
     </row>
     <row r="33" spans="1:12" ht="104.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>115</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>118</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="19"/>
@@ -2000,24 +2011,26 @@
     </row>
     <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>122</v>
-      </c>
       <c r="E34" s="15" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F34" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -2026,16 +2039,16 @@
     </row>
     <row r="35" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="18"/>
@@ -2048,16 +2061,16 @@
     </row>
     <row r="36" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="18"/>
@@ -2070,10 +2083,10 @@
     </row>
     <row r="37" spans="1:12" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="9"/>
@@ -2088,22 +2101,22 @@
     </row>
     <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -2114,20 +2127,22 @@
     </row>
     <row r="39" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>133</v>
+        <v>229</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="18"/>
-      <c r="G39" s="4"/>
+      <c r="G39" s="4" t="s">
+        <v>224</v>
+      </c>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -2136,16 +2151,16 @@
     </row>
     <row r="40" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="18"/>
@@ -2158,16 +2173,16 @@
     </row>
     <row r="41" spans="1:12" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="19"/>
@@ -2180,22 +2195,22 @@
     </row>
     <row r="42" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -2206,20 +2221,22 @@
     </row>
     <row r="43" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E43" s="16"/>
       <c r="F43" s="18"/>
-      <c r="G43" s="4"/>
+      <c r="G43" s="4" t="s">
+        <v>223</v>
+      </c>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
@@ -2228,16 +2245,16 @@
     </row>
     <row r="44" spans="1:12" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E44" s="16"/>
       <c r="F44" s="19"/>
@@ -2250,22 +2267,22 @@
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -2276,16 +2293,16 @@
     </row>
     <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="18"/>
@@ -2298,16 +2315,16 @@
     </row>
     <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="18"/>
@@ -2320,16 +2337,16 @@
     </row>
     <row r="48" spans="1:12" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E48" s="15"/>
       <c r="F48" s="19"/>
@@ -2342,22 +2359,22 @@
     </row>
     <row r="49" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -2368,20 +2385,22 @@
     </row>
     <row r="50" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E50" s="15"/>
       <c r="F50" s="18"/>
-      <c r="G50" s="4"/>
+      <c r="G50" s="4" t="s">
+        <v>223</v>
+      </c>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -2390,16 +2409,16 @@
     </row>
     <row r="51" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="18"/>
@@ -2412,16 +2431,16 @@
     </row>
     <row r="52" spans="1:12" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="19"/>
@@ -2467,12 +2486,12 @@
     </row>
     <row r="67" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
